--- a/tests/fixture_small.xlsx
+++ b/tests/fixture_small.xlsx
@@ -6,29 +6,135 @@
     <sheet name="Dashboard" sheetId="2" r:id="rId2"/>
     <sheet name="New Sales report" sheetId="3" r:id="rId3"/>
     <sheet name="Sales report Raw" sheetId="4" r:id="rId4"/>
+    <sheet name="Commission Rate by SKUs" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="1"/>
 </workbook>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AH20"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:AH40"/>
   <sheetData>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Client</t>
+          <t>Client:Project</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Customer_Type</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Client Category: Name</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>First Sale Date</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Store_Type</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Transaction Type</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Item: Full Name</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Item: Description (Sales)</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Open Balance</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Sales Rep: Name (Grouped)</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Address: Shipping Address State</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Partner: Partner Category/Role</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Commission Pct</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Transaction Status: Description</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Due Date</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Date Closed</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Primary Partner: Name</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Amount (Gross)</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Account: Name (GL-style)</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Difference</t>
+          <t>Company Name</t>
         </is>
       </c>
     </row>
@@ -44,36 +150,8 @@
       <c r="V7">
         <v>150</v>
       </c>
-      <c r="Y7">
-        <f>IF(V7&gt;0,"Y","N")</f>
-      </c>
       <c r="Z7">
         <f>V7-L7</f>
-      </c>
-      <c r="AA7">
-        <f>L7*0.05</f>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>875002 Other Store</t>
-        </is>
-      </c>
-      <c r="L8">
-        <v>10</v>
-      </c>
-      <c r="V8">
-        <v>30</v>
-      </c>
-      <c r="Y8">
-        <f>IF(V8&gt;0,"Y","N")</f>
-      </c>
-      <c r="Z8">
-        <f>V8-L8</f>
-      </c>
-      <c r="AA8">
-        <f>L8*0.05</f>
       </c>
     </row>
   </sheetData>
@@ -81,8 +159,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AH20"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:AH40"/>
   <sheetData>
     <row r="2">
       <c r="B2" t="inlineStr">
@@ -97,15 +175,105 @@
       </c>
     </row>
     <row r="3">
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Prior period</t>
-        </is>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>May/26</t>
         </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="W6">
+        <v>43.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="W7">
+        <v>50.75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="W8">
+        <v>58.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="W9">
+        <v>65.25</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="W10">
+        <v>72.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="W11">
+        <v>79.75</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="W12">
+        <v>87.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="W13">
+        <v>94.25</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="W14">
+        <v>101.5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="W15">
+        <v>108.75</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="W16">
+        <v>116.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="W17">
+        <v>123.25</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="W18">
+        <v>130.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="W19">
+        <v>137.75</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="W20">
+        <v>145.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="W21">
+        <v>152.25</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="W22">
+        <v>159.5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="W23">
+        <v>166.75</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="W24">
+        <v>174.0</v>
       </c>
     </row>
   </sheetData>
@@ -113,18 +281,133 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AH20"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:AH40"/>
   <sheetData>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Client</t>
+          <t>Client:Project</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Customer_Type</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Client Category: Name</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>First Sale Date</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Store_Type</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Transaction Type</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Item: Full Name</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Item: Description (Sales)</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Sales Rep: Name (Grouped)</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Address: Shipping Address State</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Client: Partner</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Commission Pct</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Transaction Status: Description</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Due Date</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Date Closed</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Primary Partner: Name</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Amount (Gross)</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Client Age (Years)</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>Rate</t>
+          <t>Company name</t>
         </is>
       </c>
     </row>
@@ -137,17 +420,8 @@
       <c r="L7">
         <v>42</v>
       </c>
-      <c r="Y7">
-        <v>1.5</v>
-      </c>
       <c r="Z7">
         <f>L7*2</f>
-      </c>
-      <c r="AA7">
-        <f>Z7*0.05</f>
-      </c>
-      <c r="AB7">
-        <f>AA7+1</f>
       </c>
     </row>
   </sheetData>
@@ -155,13 +429,133 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AH20"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:AH40"/>
   <sheetData>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Client</t>
+          <t>Client:Project</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Customer_Type</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Client Category: Name</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>First Sale Date</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Store_Type</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Transaction Type</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Item: Full Name</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Item: Description (Sales)</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Sales Rep: Name (Grouped)</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Address: Shipping Address State</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Client: Partner</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Commission Pct</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Transaction Status: Description</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Due Date</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Date Closed</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Primary Partner: Name</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Amount (Gross)</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Client Age (Years)</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Company name</t>
         </is>
       </c>
     </row>
@@ -177,8 +571,45 @@
       <c r="Z4">
         <f>L4*3</f>
       </c>
-      <c r="AA4">
-        <f>Z4-1</f>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:AH40"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>95302</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Fixture item</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
